--- a/data/structural_shocks.xlsx
+++ b/data/structural_shocks.xlsx
@@ -837,412 +837,412 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2590410300360014</v>
+        <v>-0.4680353224460042</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6094739914649244</v>
+        <v>-0.6859052127008773</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.416184852150198</v>
+        <v>-1.81778698732924</v>
       </c>
       <c r="E2" t="n">
-        <v>1.12107339864064</v>
+        <v>1.333415782028869</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4392774833378805</v>
+        <v>0.5081327766586109</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5555325977238261</v>
+        <v>0.5917826449218647</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05606034777093848</v>
+        <v>-0.1088168910922143</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4031762334366811</v>
+        <v>0.4798649356726946</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2542594311797707</v>
+        <v>0.1964016150593203</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2683182375010514</v>
+        <v>0.6091902361186435</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4913945064802148</v>
+        <v>-0.3381739147415123</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.05575167160740846</v>
+        <v>-0.001917872517591669</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3754182764058135</v>
+        <v>-0.1490780736949587</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5462425352346816</v>
+        <v>-0.4873022114624966</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.695312241486699</v>
+        <v>-1.638333264653165</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4530788073230463</v>
+        <v>-0.5502543150099878</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9501422233556633</v>
+        <v>1.031476312201388</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07597229749471519</v>
+        <v>-0.06517317493055019</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.02905563485035147</v>
+        <v>-0.08291266544646939</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09253782942974033</v>
+        <v>0.05189642218529658</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5605056623427604</v>
+        <v>0.6316514904434861</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.01822678739644964</v>
+        <v>0.04464620849280287</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3069373252545886</v>
+        <v>0.4038098318540462</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.231622342717597</v>
+        <v>0.08329048404778583</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5466764002025193</v>
+        <v>0.6724830985743759</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6640474627518851</v>
+        <v>0.6746199211199845</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.255611605013783</v>
+        <v>-1.152916172446296</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8555612885183506</v>
+        <v>0.6856099146061275</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.7604803934766482</v>
+        <v>-0.8278673255324117</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.09124079080460716</v>
+        <v>0.2231924596803909</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2951280170352947</v>
+        <v>0.249250567218491</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.374813689220052</v>
+        <v>1.35507245539993</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.8845805108288815</v>
+        <v>0.8436753302574447</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.7892419497229489</v>
+        <v>-0.8000523197499069</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.560532871281247</v>
+        <v>0.6463415035677554</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.1971506669939795</v>
+        <v>-0.236743509927187</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.9880690189189174</v>
+        <v>-0.9878180469378771</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.05680718343975148</v>
+        <v>0.1255034976477186</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2.751984377767447</v>
+        <v>-2.527321181586984</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.129364638945642</v>
+        <v>2.134783941816639</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.05833391858923529</v>
+        <v>-0.04266135598934717</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.0266719301345564</v>
+        <v>-0.06516638637978725</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.025556991934385</v>
+        <v>0.9076857769263639</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.205358053877109</v>
+        <v>0.9390198726689862</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1366626055134285</v>
+        <v>-0.1256821490755696</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.4087335696781352</v>
+        <v>-0.4081416673495311</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2018314083772522</v>
+        <v>0.2903218421967461</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.4079559219743684</v>
+        <v>-0.4297289150175004</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.5244378721679676</v>
+        <v>0.5122228392693166</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.2080163980190214</v>
+        <v>0.2675834541016933</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-1.33246397013228</v>
+        <v>-1.194622779830827</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.8112350237770826</v>
+        <v>0.9330556959936873</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.01944497522246387</v>
+        <v>0.05310545960633155</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.4038462150730703</v>
+        <v>-0.3263662541029107</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.532085080421893</v>
+        <v>1.355742958837183</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.1740664817685571</v>
+        <v>-0.151692568601641</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1875947946819294</v>
+        <v>0.08997469373025688</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.8833680420858824</v>
+        <v>0.9353648994072585</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.2233013072099646</v>
+        <v>0.209701589098085</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1463650567974963</v>
+        <v>0.1052763574962414</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.3503043989982588</v>
+        <v>0.3425046515329005</v>
       </c>
       <c r="BK2" t="n">
-        <v>-1.579733674144625</v>
+        <v>-1.439136980057998</v>
       </c>
       <c r="BL2" t="n">
-        <v>-1.648541897371377</v>
+        <v>-1.578641625355143</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.3335850733681603</v>
+        <v>0.2702056600900642</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.207281297836728</v>
+        <v>1.342924533037815</v>
       </c>
       <c r="BO2" t="n">
-        <v>-1.091943725049678</v>
+        <v>-0.9005449773813683</v>
       </c>
       <c r="BP2" t="n">
-        <v>-2.440463911770409</v>
+        <v>-2.33512743412808</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-3.973556666017935</v>
+        <v>-3.830003202795267</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.2813839310204657</v>
+        <v>-0.2946475047659619</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.14920231865678</v>
+        <v>1.257849763072156</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.043479809846034</v>
+        <v>0.939522828696795</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.9625521788012418</v>
+        <v>1.065593430934081</v>
       </c>
       <c r="BV2" t="n">
-        <v>-1.048170034503323</v>
+        <v>-1.002111256441349</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.6159258830887402</v>
+        <v>0.702985831022769</v>
       </c>
       <c r="BX2" t="n">
-        <v>2.069789994543287</v>
+        <v>2.201198321815879</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.6463373733889647</v>
+        <v>-0.5933475720834419</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.3754950579008449</v>
+        <v>0.5581288182777961</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.146618224910109</v>
+        <v>2.203830351629002</v>
       </c>
       <c r="CB2" t="n">
-        <v>1.252941854597066</v>
+        <v>0.8601347790471386</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.2237424169170612</v>
+        <v>-0.162330270267615</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.2235342424668249</v>
+        <v>-0.1968290209347674</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.7628419959289434</v>
+        <v>-0.9330760043434189</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0.7030357978329909</v>
+        <v>-0.8723072719669862</v>
       </c>
       <c r="CG2" t="n">
-        <v>1.019416129645313</v>
+        <v>1.139437980861534</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.2007781544823965</v>
+        <v>-0.0953798819082767</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.6367198569715025</v>
+        <v>0.7995854257595232</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.682963259436103</v>
+        <v>1.62627773541396</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.1235940656516454</v>
+        <v>0.09385290052417859</v>
       </c>
       <c r="CL2" t="n">
-        <v>-1.155091802431207</v>
+        <v>-1.184238252081599</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.5914667796634239</v>
+        <v>-0.7032559445821522</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.3633600907855549</v>
+        <v>-0.3506383970083581</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.2414867445845364</v>
+        <v>-0.1927955397905379</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.1838726965924576</v>
+        <v>-0.1085767920254857</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1411651197018504</v>
+        <v>0.04056255600382127</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.4459936773041498</v>
+        <v>-0.365737275888559</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0.2192630743470188</v>
+        <v>-0.09949775894415969</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0.7837597765060047</v>
+        <v>-0.8370204989747303</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.9342405967894175</v>
+        <v>1.13117858609812</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.7832831717036538</v>
+        <v>0.8715812953631621</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.3901650051144012</v>
+        <v>-0.3813215828255572</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0.7607424451514151</v>
+        <v>-0.8055868759639536</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.2040141887801484</v>
+        <v>-0.6496956248990116</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.5874929811776397</v>
+        <v>-0.3494837439055414</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.7719516121576254</v>
+        <v>0.6974327989491125</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.2877547956330996</v>
+        <v>0.4422143258713935</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0.2014386165740156</v>
+        <v>-0.1003897033986506</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.2949313768075719</v>
+        <v>0.05300380101152186</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.4722074848356401</v>
+        <v>-0.6112094947160081</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.4968933167272252</v>
+        <v>-0.4473463059010761</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.2031601664878481</v>
+        <v>0.006506966701405441</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.3868218689380881</v>
+        <v>-0.5847615627944058</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.50903519996536</v>
+        <v>-0.4910389722443773</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.9728463864985543</v>
+        <v>1.013185026521199</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0.03624592234545372</v>
+        <v>0.09579306653351352</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0.07834478066011917</v>
+        <v>-0.09162624222208191</v>
       </c>
       <c r="DM2" t="n">
-        <v>1.029284296765667</v>
+        <v>0.9133539888696079</v>
       </c>
       <c r="DN2" t="n">
-        <v>-1.612488441721365</v>
+        <v>-1.598099955241798</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.3297351503484508</v>
+        <v>-0.3050266074704037</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0.3990189979536006</v>
+        <v>-0.5639516088683005</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.8220853913123761</v>
+        <v>-0.9073940872084795</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.6280230147529844</v>
+        <v>0.4011490568747942</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.04697176965431468</v>
+        <v>-0.2688991204933996</v>
       </c>
       <c r="DT2" t="n">
-        <v>2.110619593618015</v>
+        <v>2.076087143039967</v>
       </c>
       <c r="DU2" t="n">
-        <v>-2.138049360929691</v>
+        <v>-2.275758577311479</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.8555232350656896</v>
+        <v>-0.9291904949251876</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.6932927281943599</v>
+        <v>-0.5690089562478526</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.06676228407522741</v>
+        <v>-0.05924333750544925</v>
       </c>
       <c r="DY2" t="n">
-        <v>1.15238070048225</v>
+        <v>1.051832016328795</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-1.471202759653818</v>
+        <v>-1.423495859523985</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.3079788546976797</v>
+        <v>-0.3241601765058832</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.3335547828166571</v>
+        <v>-0.155276789021367</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0.56910295057666</v>
+        <v>-0.3204268439138477</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.421711262025939</v>
+        <v>1.515820365514419</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.7467116547359748</v>
+        <v>-0.894797577854446</v>
       </c>
       <c r="EF2" t="n">
-        <v>3.807840526114463</v>
+        <v>3.879447579538007</v>
       </c>
       <c r="EG2" t="n">
-        <v>-1.06312190356209</v>
+        <v>-0.9154243525995867</v>
       </c>
     </row>
     <row r="3">
@@ -1252,412 +1252,412 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.991169476354503</v>
+        <v>-1.530284165233097</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.153135661209496</v>
+        <v>-0.2529622233730924</v>
       </c>
       <c r="D3" t="n">
-        <v>1.227526749817197</v>
+        <v>1.669281985870888</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7852656049687867</v>
+        <v>1.410672561706929</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2981011778172299</v>
+        <v>-0.08665388408691792</v>
       </c>
       <c r="G3" t="n">
-        <v>1.388858020121559</v>
+        <v>1.153179018529764</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8538003414102179</v>
+        <v>0.9706956993924496</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4730156340788367</v>
+        <v>-0.6072677559198535</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5295715690486392</v>
+        <v>-0.6442677338158883</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.16584891811585</v>
+        <v>-0.004737182061133122</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2286962990702134</v>
+        <v>0.1584851066765061</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9357519261410218</v>
+        <v>-1.022986864268311</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1391953085361697</v>
+        <v>-0.1930062923007253</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2936843144250081</v>
+        <v>-0.6238557238667922</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.297763702727064</v>
+        <v>-0.465193813771018</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2135276188882116</v>
+        <v>-1.02422019610105</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.04009868325916608</v>
+        <v>0.1247482168902271</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3960518036969176</v>
+        <v>0.8497475748999584</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1870622700933678</v>
+        <v>-0.1932426813256659</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3811108340458182</v>
+        <v>0.6414255295302399</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.06199382871134766</v>
+        <v>-0.1110185823352352</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2089413239311064</v>
+        <v>-0.01508466621082674</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9741563240181317</v>
+        <v>1.009013305260018</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.654853196460821</v>
+        <v>-0.5272614886610973</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9987449321322108</v>
+        <v>0.874361562749669</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.4162891515116544</v>
+        <v>-0.4464520448182274</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.020015916318087</v>
+        <v>0.9036118057787237</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.370911367909909</v>
+        <v>0.6723495703619302</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.130655345378203</v>
+        <v>-1.185008033661778</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.1253092577232518</v>
+        <v>0.2142908996069174</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.07657030063710588</v>
+        <v>-0.5758524960267496</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4319629022049685</v>
+        <v>0.8013427519950154</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6320146528554037</v>
+        <v>0.5740964469684067</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.05743142326841687</v>
+        <v>-0.01235665375144487</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1084415406449323</v>
+        <v>0.1896329916678934</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3822931768503846</v>
+        <v>0.4077881494824181</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.2537027225016615</v>
+        <v>-0.3315303883616952</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.2202629490507873</v>
+        <v>0.3286232698398347</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6384980570351452</v>
+        <v>0.04332927412225694</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.6416896460242395</v>
+        <v>-0.8145577595507844</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1407348567913998</v>
+        <v>0.03136595606603255</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.5930178796878892</v>
+        <v>-0.3612556405215518</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.4042478764265112</v>
+        <v>-0.4337075419371999</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.3112050250755641</v>
+        <v>-0.0332839539729804</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.6847054154883889</v>
+        <v>-0.5527517578050422</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.3029308242799735</v>
+        <v>-0.3302229104398122</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.6117755550785279</v>
+        <v>-0.7037708087730449</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.04446755627904907</v>
+        <v>-0.1751474625744978</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4584199679883161</v>
+        <v>0.2349787995958577</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.01569785858338949</v>
+        <v>0.03187104264067391</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.4770245999778065</v>
+        <v>0.3409382458149336</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.1647714982411309</v>
+        <v>-0.5423593056268813</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0805869446105372</v>
+        <v>0.01216286504411098</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1919117490665797</v>
+        <v>-0.01942588875493779</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.4536407498858521</v>
+        <v>-0.6815442220661228</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.08421243285976494</v>
+        <v>-0.3116516818665361</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1251819790113041</v>
+        <v>0.03618447126319695</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.2025508637617782</v>
+        <v>-0.2126032501148696</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.5116332024485893</v>
+        <v>0.4060848440216522</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.09441753173147199</v>
+        <v>0.2275244485163261</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.368507912063542</v>
+        <v>0.3835765926923985</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.3588835045109094</v>
+        <v>0.3948518614494025</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.3997098301120644</v>
+        <v>-0.593092530092916</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.04217290413315703</v>
+        <v>-0.1216652222662478</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.9606848029396048</v>
+        <v>0.4695014774686402</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.8021919337996453</v>
+        <v>0.9500244661501532</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.7564717598953192</v>
+        <v>0.5927361519894383</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.3111807036772789</v>
+        <v>-0.03025551207759777</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.2393569739513167</v>
+        <v>0.8862295777230996</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.698593437026058</v>
+        <v>1.732962172157055</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.004896929949088271</v>
+        <v>-0.1476434465361238</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.2392379294009856</v>
+        <v>-0.1418959730574103</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.06999000478092368</v>
+        <v>0.08375830459848159</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.2201727843004476</v>
+        <v>0.2760292850037674</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.375309668585948</v>
+        <v>0.07248788573248138</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.050356685703041</v>
+        <v>1.186988768230644</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.483576262891016</v>
+        <v>0.6041887466391477</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.2859548257158557</v>
+        <v>0.3264561089487314</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.9592568365204958</v>
+        <v>-0.7215527099108439</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.008486419915288871</v>
+        <v>0.1113189221640627</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0886846732280604</v>
+        <v>-0.2494767035376593</v>
       </c>
       <c r="CE3" t="n">
-        <v>-1.491668964767749</v>
+        <v>-1.216803953368816</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.3442041428816771</v>
+        <v>0.6348389994161336</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.8505241870455824</v>
+        <v>0.6663504546265833</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01218189578295261</v>
+        <v>-0.194184495324996</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.5499914439532213</v>
+        <v>0.06005763386780963</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.6842075771291917</v>
+        <v>-0.6068788780745289</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.3900038367298966</v>
+        <v>0.3515744006912906</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1990326077509625</v>
+        <v>0.02794555691927045</v>
       </c>
       <c r="CM3" t="n">
-        <v>8.972473394028082</v>
+        <v>8.892824118893179</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.7896012750835577</v>
+        <v>-1.006402718763649</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.6130075164107601</v>
+        <v>-0.6713174640338367</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.8177979039909626</v>
+        <v>-0.8173216018662522</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.4189573826181933</v>
+        <v>0.6552672833395664</v>
       </c>
       <c r="CR3" t="n">
-        <v>-1.040731567159342</v>
+        <v>-1.048983202464969</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.9435836505710856</v>
+        <v>-0.7594594130716259</v>
       </c>
       <c r="CT3" t="n">
-        <v>-1.263679340354245</v>
+        <v>-1.272355762157513</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0.7879869559900999</v>
+        <v>-0.6843292214771759</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.524957474679642</v>
+        <v>0.8891585638044958</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2088060851134022</v>
+        <v>0.4117348000445329</v>
       </c>
       <c r="CX3" t="n">
-        <v>-1.162312063493453</v>
+        <v>-0.9377545285014304</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.086754274895846</v>
+        <v>0.6144299830894959</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-1.328596101595194</v>
+        <v>-1.511567573502035</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.649838413774423</v>
+        <v>-0.7168564985699015</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.234831787561923</v>
+        <v>0.1000497314906909</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.1929743197046453</v>
+        <v>-0.318581810692193</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0.001919089855139322</v>
+        <v>-0.207268903495775</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.3427954163477679</v>
+        <v>-0.1396993644461872</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.5324254880491671</v>
+        <v>0.2888513544857711</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.3267238270329574</v>
+        <v>-0.3244084503903735</v>
       </c>
       <c r="DH3" t="n">
-        <v>-2.071595432432639</v>
+        <v>-1.533583924751277</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2006298618147503</v>
+        <v>-0.2988914608208702</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2096749726298942</v>
+        <v>0.4734816719699316</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0452870362237793</v>
+        <v>-0.3931599236232388</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.3080991357620196</v>
+        <v>-0.1154091037404692</v>
       </c>
       <c r="DM3" t="n">
-        <v>-1.192641459655647</v>
+        <v>-0.9850841742802239</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.4848431177186083</v>
+        <v>-0.5678270522792896</v>
       </c>
       <c r="DO3" t="n">
-        <v>-1.018708126142336</v>
+        <v>-1.232826412599825</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.3526646476899171</v>
+        <v>-0.5890051309215122</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1117417870948981</v>
+        <v>0.2197054209029336</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.3412009190728802</v>
+        <v>0.007500666629350615</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.5160931052933031</v>
+        <v>0.6514194877424003</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.3799879470411128</v>
+        <v>0.8028934940587807</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.2069419645257193</v>
+        <v>0.0943830632527253</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0.4458465888976925</v>
+        <v>-0.1630048136188686</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.5129593685150194</v>
+        <v>-0.4576194713810898</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.2906131605153461</v>
+        <v>-0.4612365512676957</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.6778470447438989</v>
+        <v>-0.6187386692071877</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0.0163153882118034</v>
+        <v>-0.1141354435992183</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.8018833662598098</v>
+        <v>-0.4997291879829095</v>
       </c>
       <c r="EB3" t="n">
-        <v>-1.012008069349038</v>
+        <v>-1.001086600788615</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.765630617983742</v>
+        <v>0.3235386573421566</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.09304147667919455</v>
+        <v>0.08655295522000234</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0.3287091381671552</v>
+        <v>-0.2856448150215704</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.1340501187518995</v>
+        <v>-0.2931687662120785</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.2292976678123959</v>
+        <v>0.4339774807034161</v>
       </c>
     </row>
     <row r="4">
@@ -1667,412 +1667,412 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.647677064994649</v>
+        <v>-2.290244473768637</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4436189066581101</v>
+        <v>0.6675623104868772</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4811778377954983</v>
+        <v>-0.6727649559161668</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.361542229530612</v>
+        <v>-3.452489813444828</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.136053820225198</v>
+        <v>-3.010272297791217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5667824464705156</v>
+        <v>1.236747750803118</v>
       </c>
       <c r="H4" t="n">
-        <v>1.636981683152022</v>
+        <v>0.9135083996872864</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2955281233210909</v>
+        <v>-0.04544389561642831</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06072404281827656</v>
+        <v>0.04873469160956893</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2514968739693683</v>
+        <v>-0.601601926013609</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9155456365231089</v>
+        <v>-0.7354492732800064</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.398260207109843</v>
+        <v>-1.044114724403975</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4493692720965182</v>
+        <v>-0.3274151268530806</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6293510451384468</v>
+        <v>-0.06086850354235025</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.05198319361232859</v>
+        <v>0.2464106632107781</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.07748745242517818</v>
+        <v>1.433641945329557</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6708262931651471</v>
+        <v>0.4674292151815955</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5494286318450958</v>
+        <v>-0.06680844220795613</v>
       </c>
       <c r="T4" t="n">
-        <v>0.160768012820829</v>
+        <v>-0.1245594663264572</v>
       </c>
       <c r="U4" t="n">
-        <v>1.202765629826445</v>
+        <v>0.6537838222020973</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3254352581856624</v>
+        <v>-0.1873400776741393</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1301932615467981</v>
+        <v>0.4831869641730947</v>
       </c>
       <c r="X4" t="n">
-        <v>1.544745031885133</v>
+        <v>1.223584139536943</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.6056569573715309</v>
+        <v>-0.7821569118741699</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.727045921961332</v>
+        <v>1.611823177974961</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.8187599354448498</v>
+        <v>-0.7206834514643544</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.979881595984102</v>
+        <v>1.569811748077879</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.236909696749408</v>
+        <v>0.4435808754466549</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.3666350294783227</v>
+        <v>-0.2220318917594163</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.05744019561530858</v>
+        <v>-0.3585090346716849</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3980938723518093</v>
+        <v>0.7912147837830323</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.7117133097009242</v>
+        <v>0.09769782452079233</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.018374687021181</v>
+        <v>1.11068865523848</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.341714192001387</v>
+        <v>0.5655157541917479</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.045705868482056</v>
+        <v>0.7912520474561143</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8194841622922403</v>
+        <v>0.6124615350802735</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01881883727518299</v>
+        <v>0.08485756764317344</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.109973248594202</v>
+        <v>0.5843128723815704</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7086077250792636</v>
+        <v>1.309423997182941</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.205648737248854</v>
+        <v>0.07181684195946836</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.8284218616591886</v>
+        <v>0.8772446287101623</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.088819963855667</v>
+        <v>-1.016316929950235</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.748980203071727</v>
+        <v>0.3902493161813064</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.3146272944371581</v>
+        <v>-0.7368198093057583</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.3593496553861987</v>
+        <v>-0.5569960653421225</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.1296845007422984</v>
+        <v>-0.06082824224538835</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.4651602827498616</v>
+        <v>-0.2645124467937902</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.003295535319601286</v>
+        <v>0.02060764183566651</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.8303886843576161</v>
+        <v>0.9047173318642516</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.2044891075780579</v>
+        <v>-0.2363771621379415</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.005064298939354761</v>
+        <v>0.295172634128378</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.7037479216786969</v>
+        <v>0.09955460738335833</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.04958564041642572</v>
+        <v>0.05918553328247043</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.1704480560164618</v>
+        <v>0.3650607365857591</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.08408714344015143</v>
+        <v>-0.02147272965169968</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1316279905733667</v>
+        <v>0.76208268208964</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.5163161839211404</v>
+        <v>0.5813916518026556</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.2636760872672769</v>
+        <v>0.2756297770646952</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.720612564405395</v>
+        <v>0.818426796626025</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.7304494395415733</v>
+        <v>0.07646733927849743</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.9321071733963269</v>
+        <v>0.8712794868357513</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.6314701841872038</v>
+        <v>0.4449173038914602</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.04206860958941359</v>
+        <v>0.1169986091454009</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.7238828711058676</v>
+        <v>0.3562588839270868</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.7145204602835268</v>
+        <v>1.346715483593461</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.5641579691381581</v>
+        <v>-0.321836286049011</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.3234617938596521</v>
+        <v>0.3765806983814144</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0.330878411978472</v>
+        <v>-0.530500466582615</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.07709448596978093</v>
+        <v>-1.060097641060284</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.4274988170224522</v>
+        <v>0.5377639023891783</v>
       </c>
       <c r="BT4" t="n">
-        <v>-1.770902987273688</v>
+        <v>-1.124042484239392</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.518705998162529</v>
+        <v>-0.4638712925373883</v>
       </c>
       <c r="BV4" t="n">
-        <v>-1.050138273547689</v>
+        <v>-1.081385297772618</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0.9651328218707811</v>
+        <v>-1.634563502857821</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.8600109677618917</v>
+        <v>-0.2844484140660398</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.7567442024782917</v>
+        <v>0.5349885369746623</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.3968379491193966</v>
+        <v>0.2747556170175321</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0.1492928168390436</v>
+        <v>0.2292501649583302</v>
       </c>
       <c r="CB4" t="n">
-        <v>-1.492048316404055</v>
+        <v>-1.920173240863368</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0.5002752323231335</v>
+        <v>-0.4089599593221636</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0.02183942616479697</v>
+        <v>0.5639270063842674</v>
       </c>
       <c r="CE4" t="n">
-        <v>-1.277870296782696</v>
+        <v>-1.628501159967937</v>
       </c>
       <c r="CF4" t="n">
-        <v>-0.08935023709931675</v>
+        <v>-1.792259453539474</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.4736364928370115</v>
+        <v>0.8122778989469018</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.7679573893901545</v>
+        <v>-0.4101728642601388</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0.3645546210362405</v>
+        <v>0.3442972034727966</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0.6492876804188342</v>
+        <v>-0.8080204324482405</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.7858463447911598</v>
+        <v>0.8443219382842971</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.6783105244161602</v>
+        <v>0.8942551902513104</v>
       </c>
       <c r="CM4" t="n">
-        <v>-4.438361257019632</v>
+        <v>-2.552610900348299</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.254295398448455</v>
+        <v>2.045292014484358</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.7601887507951713</v>
+        <v>0.6164564359072954</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.4955745993143422</v>
+        <v>-0.3800936333664132</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.418210690234045</v>
+        <v>0.5151254842901478</v>
       </c>
       <c r="CR4" t="n">
-        <v>-1.029047211504796</v>
+        <v>-0.9263228697102763</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0.4102657897444317</v>
+        <v>-0.747751497441861</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0.4380854071311184</v>
+        <v>-0.5194959396393518</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.1205247005036998</v>
+        <v>-0.1813806666799267</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.126674300287298</v>
+        <v>0.251531347424898</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.8843110124844888</v>
+        <v>0.235413367381488</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.2183496633057229</v>
+        <v>-0.3248271905145961</v>
       </c>
       <c r="CY4" t="n">
-        <v>4.455628059270621</v>
+        <v>4.904600570230724</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.2152874928094962</v>
+        <v>0.05603781631834892</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.4369414748142492</v>
+        <v>0.4366176354188592</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.9224806455439771</v>
+        <v>1.101173348621028</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0.6859567966630039</v>
+        <v>-0.3361553744918709</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.2618221686620569</v>
+        <v>0.4953705207213633</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0.2042735648613239</v>
+        <v>-0.5726195274863707</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.5570387414333227</v>
+        <v>0.8773415013226175</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0.1561452529056091</v>
+        <v>-0.1152468678324885</v>
       </c>
       <c r="DH4" t="n">
-        <v>-1.852950265434721</v>
+        <v>-2.477170279808039</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.6704921474506335</v>
+        <v>1.412386917903886</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.977999324023019</v>
+        <v>0.3263020417175608</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.002249011638230238</v>
+        <v>0.8058025790027246</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.3465439841702674</v>
+        <v>0.4925144267226274</v>
       </c>
       <c r="DM4" t="n">
-        <v>-0.9228727953605522</v>
+        <v>-1.115228996312396</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0.4874824943233735</v>
+        <v>-0.3731428954456089</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.9680602542334773</v>
+        <v>-0.5511076008968375</v>
       </c>
       <c r="DP4" t="n">
-        <v>-0.08244592453974899</v>
+        <v>0.3483945614067589</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.1156951045710168</v>
+        <v>-0.004441098424581148</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.4516135324324728</v>
+        <v>-0.8905843666743247</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.6496328652218787</v>
+        <v>0.4997326722861978</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0.1449334268508343</v>
+        <v>-0.6001603283168248</v>
       </c>
       <c r="DU4" t="n">
-        <v>-0.1496923835004027</v>
+        <v>-0.7624531108053364</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0.2281748327037341</v>
+        <v>-0.7311301375830365</v>
       </c>
       <c r="DW4" t="n">
-        <v>-0.286429055805334</v>
+        <v>0.08070496914000225</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.7550413629870186</v>
+        <v>-0.7004489167205915</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0.49468422650594</v>
+        <v>-0.3456158418407559</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.3440400614485886</v>
+        <v>0.4531088799581169</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.2352380504424424</v>
+        <v>-0.762441888886252</v>
       </c>
       <c r="EB4" t="n">
-        <v>-1.138157794953006</v>
+        <v>-0.9998014543841368</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.349746933721361</v>
+        <v>0.9526135543948522</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0.09490906527722447</v>
+        <v>-0.06493989892545925</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0.08408862236233519</v>
+        <v>-0.1947866235208187</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.1076209635124521</v>
+        <v>0.9648528308278349</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.3611607810448729</v>
+        <v>-0.6699316062680497</v>
       </c>
     </row>
     <row r="5">
@@ -2082,412 +2082,412 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.238748964171009</v>
+        <v>0.7437569925375339</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.8172797451909303</v>
+        <v>-0.4622905792607978</v>
       </c>
       <c r="D5" t="n">
-        <v>1.271459796770199</v>
+        <v>0.295705419213411</v>
       </c>
       <c r="E5" t="n">
-        <v>1.178292385178517</v>
+        <v>-0.4968386125899602</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4706356410273816</v>
+        <v>-1.011030362344769</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9469283980299099</v>
+        <v>-0.7477247474418797</v>
       </c>
       <c r="H5" t="n">
-        <v>1.411362490942478</v>
+        <v>1.666082168405717</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7007099075864807</v>
+        <v>-0.6406308419063687</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1087716553904967</v>
+        <v>0.007202551953617983</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5145916239646007</v>
+        <v>0.6943424837099703</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1369797582257979</v>
+        <v>-0.4854539854141448</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8142438752129831</v>
+        <v>-1.168424507593762</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4170323603730757</v>
+        <v>-0.3909892224161363</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.236621678171926</v>
+        <v>-1.354538070512911</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8262496036189981</v>
+        <v>-0.7700560845283141</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.38239672176982</v>
+        <v>-3.2717893744171</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2179686403674508</v>
+        <v>0.4445550737424253</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8732458199425</v>
+        <v>1.809679137597764</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3257173606748704</v>
+        <v>0.2951066122906967</v>
       </c>
       <c r="U5" t="n">
-        <v>1.246866390383305</v>
+        <v>1.505151625861835</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2869104161206505</v>
+        <v>-0.3594455080722397</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7832913607993625</v>
+        <v>-0.6897165065675137</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6257868076007859</v>
+        <v>1.147653078646516</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5360248237934233</v>
+        <v>0.1639656355882159</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007895825451812012</v>
+        <v>0.7006219704933045</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.05340242436742919</v>
+        <v>-0.3417721625464036</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6299704277137571</v>
+        <v>1.336881997498323</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.815734568295222</v>
+        <v>2.02373287267018</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.6359586223333714</v>
+        <v>-0.7132290909832371</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.7649139186739738</v>
+        <v>0.9366051650783637</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1.241313669619956</v>
+        <v>-0.9398161142727469</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.433177192322752</v>
+        <v>1.541209159283505</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.1843238643082296</v>
+        <v>0.1419253516754004</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.5528248073595752</v>
+        <v>-0.4349239929767945</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2958233387464872</v>
+        <v>0.8202243696351053</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.4614738935959367</v>
+        <v>0.6787860905993578</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.2834116682719554</v>
+        <v>-0.2414294479745779</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9096165432564023</v>
+        <v>1.399508037059944</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1.566600096028725</v>
+        <v>-1.066426396389151</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.8736507342117369</v>
+        <v>-0.552567831761696</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.4076714784468941</v>
+        <v>-0.02352541368941904</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.1275861399439502</v>
+        <v>-0.1153111737709921</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.2329337512012719</v>
+        <v>0.6784601337099044</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.183473634087308</v>
+        <v>0.8173206797471698</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.4587866290850138</v>
+        <v>0.1776786397016122</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.2685567938848867</v>
+        <v>-0.2460617853437854</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.6126056520109416</v>
+        <v>-0.4852598723477521</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.1217538461647307</v>
+        <v>-0.05373740880939844</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.2900671047575251</v>
+        <v>0.1111260565446086</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.05894908154961667</v>
+        <v>0.0726081448990241</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.6662750833524558</v>
+        <v>-0.5983735927396463</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1.809046055340731</v>
+        <v>-1.745802527022232</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.1285508955792507</v>
+        <v>-0.102417349648684</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.9684996105072765</v>
+        <v>-0.7744901796350209</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.09321830462146038</v>
+        <v>-0.003165594660444512</v>
       </c>
       <c r="BE5" t="n">
-        <v>-1.464599429619275</v>
+        <v>-1.282528570270871</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1404188116991273</v>
+        <v>-0.000546201569825372</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1893194413273372</v>
+        <v>0.07677547113055198</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.192773547748745</v>
+        <v>0.0430981052242501</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.319799280091625</v>
+        <v>1.523345739646608</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.04283574713587852</v>
+        <v>0.3889560603865021</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.2597233144500224</v>
+        <v>0.5398262174469429</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.5769621343781048</v>
+        <v>-0.4226455904668478</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7032061183641717</v>
+        <v>0.9327834074328155</v>
       </c>
       <c r="BN5" t="n">
-        <v>-1.440300828271774</v>
+        <v>-1.163778563768133</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.08823320917056428</v>
+        <v>-0.1797594582649713</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.2454783384045335</v>
+        <v>-0.3605958459162826</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.4825204710544858</v>
+        <v>0.2018161866612995</v>
       </c>
       <c r="BR5" t="n">
-        <v>2.411498139531358</v>
+        <v>1.983943051868662</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.1999720020551106</v>
+        <v>0.05272118017784776</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.8190135615901161</v>
+        <v>-1.75698581485989</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.1061511725947383</v>
+        <v>-0.2918554211830723</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.4263008216002243</v>
+        <v>-0.2075651382024103</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.720315570725071</v>
+        <v>1.176353678273432</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.9878124234924782</v>
+        <v>-1.228220424398741</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.6405364453044364</v>
+        <v>0.7267669493557143</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.1680775460742465</v>
+        <v>0.3024545643925797</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.4266723405292441</v>
+        <v>-0.2033951646298261</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.048706858397994</v>
+        <v>0.09766311401981995</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.1150250578563382</v>
+        <v>-0.3909337022525856</v>
       </c>
       <c r="CD5" t="n">
-        <v>-1.204474170745033</v>
+        <v>-1.106935262211634</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.769639318901112</v>
+        <v>0.2128406800036158</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.909210571352799</v>
+        <v>3.333312886534552</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.6535835009203191</v>
+        <v>-0.4151851322423579</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.6831532597742718</v>
+        <v>-0.8499871000632271</v>
       </c>
       <c r="CI5" t="n">
-        <v>-1.540199810437275</v>
+        <v>-1.49519230953249</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.4122458262411615</v>
+        <v>0.2623461134631855</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.3067135306305252</v>
+        <v>0.06483630643294581</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.6605252995391576</v>
+        <v>-0.4242557320355105</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.1583972752879591</v>
+        <v>-3.730020246453904</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.4659642728340323</v>
+        <v>0.8422846194251117</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.1921785007172365</v>
+        <v>0.3791689591166338</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.4615335097892546</v>
+        <v>-0.4075501516851011</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.822744117512649</v>
+        <v>2.209907532581941</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.4845570228310233</v>
+        <v>-0.572682559693795</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.395507046409973</v>
+        <v>0.5417751394389778</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.1409545988831421</v>
+        <v>-0.08585692644994901</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.1472235039289162</v>
+        <v>0.6475071786351921</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.836588512579092</v>
+        <v>2.262220881599833</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.306192166742901</v>
+        <v>1.57608803676313</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.7896108311155009</v>
+        <v>0.8877936337733178</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.8221188688410749</v>
+        <v>0.3788557756196511</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-1.641720792622784</v>
+        <v>-1.189967560062805</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0765587420809847</v>
+        <v>0.2074011272141605</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.6844401268095316</v>
+        <v>-0.05461164889216261</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.7457329855459044</v>
+        <v>-0.8303383959313517</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.4430868765054519</v>
+        <v>-0.4646237221319623</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.8257521386148545</v>
+        <v>0.5946098404497017</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.7531295888660223</v>
+        <v>-0.4882983194721189</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.03936122155639794</v>
+        <v>-0.1229351250721705</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.299198145782946</v>
+        <v>0.5444196788425989</v>
       </c>
       <c r="DI5" t="n">
-        <v>-1.889657619837198</v>
+        <v>-1.443240275286874</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.297358049626891</v>
+        <v>1.604186427036374</v>
       </c>
       <c r="DK5" t="n">
-        <v>-1.761603956893562</v>
+        <v>-1.255194095914539</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.6705976491713532</v>
+        <v>-0.4540111789520586</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.4349149777945633</v>
+        <v>0.1604182950235051</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.3996004945910251</v>
+        <v>-0.5110783338613167</v>
       </c>
       <c r="DO5" t="n">
-        <v>-1.079252272154949</v>
+        <v>-1.188093878806002</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.9665069852138556</v>
+        <v>-0.9784654517927397</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.2941938116862067</v>
+        <v>0.1603363066626309</v>
       </c>
       <c r="DR5" t="n">
-        <v>1.230974162427426</v>
+        <v>0.777584847340945</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.5327833425571235</v>
+        <v>0.4425579283022906</v>
       </c>
       <c r="DT5" t="n">
-        <v>1.26170727266585</v>
+        <v>1.027232617705844</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.530544623929788</v>
+        <v>1.140872239627295</v>
       </c>
       <c r="DV5" t="n">
-        <v>1.065499780129777</v>
+        <v>0.6868785735582846</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.7337481032776569</v>
+        <v>-0.4547271363057328</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.2574050904428261</v>
+        <v>-0.6771475302111851</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.2948676320910568</v>
+        <v>-0.4753127901442282</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.3869026816741966</v>
+        <v>-0.214537135730759</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.043064597845082</v>
+        <v>0.9608941875069698</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.5122561070201984</v>
+        <v>-0.6209683255479082</v>
       </c>
       <c r="EC5" t="n">
-        <v>-1.427874826523858</v>
+        <v>-1.067545388000141</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.0354063207093297</v>
+        <v>0.05988193968033734</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.2688348780131065</v>
+        <v>0.09574631827335803</v>
       </c>
       <c r="EF5" t="n">
-        <v>-2.014798914069192</v>
+        <v>-1.623780229057722</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.8364700058153628</v>
+        <v>0.660238930190166</v>
       </c>
     </row>
     <row r="6">
@@ -2497,412 +2497,412 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3069421244524381</v>
+        <v>0.6390306393620272</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04522986726241712</v>
+        <v>-0.07482040646958901</v>
       </c>
       <c r="D6" t="n">
-        <v>2.362596745485501</v>
+        <v>2.383156704759115</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.097089623213838</v>
+        <v>-0.9505718532680402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5136711520758174</v>
+        <v>0.2841600914660336</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2816360128256025</v>
+        <v>0.001661545354647633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8756491394724607</v>
+        <v>0.9966863165145444</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1948793995397902</v>
+        <v>-0.3158860852814266</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3685045659783911</v>
+        <v>0.4248274983207202</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.460745557608192</v>
+        <v>-2.379091661533329</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6928619583907901</v>
+        <v>-0.7511342515040368</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2840815414788349</v>
+        <v>0.1936824439271097</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.214220248808591</v>
+        <v>-1.338594082902431</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3260415788142357</v>
+        <v>0.07396922495190864</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2710519435601262</v>
+        <v>-0.0804395539423373</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.332902997059777</v>
+        <v>1.739049064075183</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1876775277956247</v>
+        <v>-0.03803920775708267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0121555234428772</v>
+        <v>0.646749431832867</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6187650981840943</v>
+        <v>0.5747619161192242</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1804036314447995</v>
+        <v>0.04374392363112582</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1562741260288159</v>
+        <v>-0.1582623643759875</v>
       </c>
       <c r="W6" t="n">
-        <v>0.132157183587417</v>
+        <v>-0.00762003828425525</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8335186764299588</v>
+        <v>-0.7382268044622549</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23693395466982</v>
+        <v>1.362272152963439</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.8818993414814652</v>
+        <v>-0.898289320714222</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.183845575764391</v>
+        <v>0.2901809329785385</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.014271760892221</v>
+        <v>-1.165900526291215</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4331298618865134</v>
+        <v>0.8212438551098177</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.466658750079605</v>
+        <v>0.9432288610482835</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.827681605802771</v>
+        <v>-1.319928056735242</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.5919041414882605</v>
+        <v>0.4630352764386556</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.5194928948292845</v>
+        <v>-0.1353465495848916</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.364286501647224</v>
+        <v>0.4647261244822014</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.5195670021549554</v>
+        <v>0.3340661242056218</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.8027364015106051</v>
+        <v>-0.6632236725993776</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.06332332747349255</v>
+        <v>0.1334258115727684</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.238771540486242</v>
+        <v>0.03689752280195905</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1.117477972848289</v>
+        <v>-0.9595608449040784</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1.182270321711641</v>
+        <v>-1.802371618294185</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.3883806959019584</v>
+        <v>-0.1140549741209187</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.2176579439339107</v>
+        <v>-0.1507630159009024</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.5502683386878607</v>
+        <v>-0.1211782578874324</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.08229613974883927</v>
+        <v>0.333618512783131</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.047817319723749</v>
+        <v>1.392298060789757</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.552028415154933</v>
+        <v>1.624091160021599</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.03386734017470372</v>
+        <v>-0.1578736360825334</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.8096897711673575</v>
+        <v>-0.7687963312970122</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.162340514930345</v>
+        <v>-0.2093369901134132</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.2738185312384016</v>
+        <v>-0.2627712609630675</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.6191686651625917</v>
+        <v>-0.5340465122314187</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.7018787051805361</v>
+        <v>-0.9885181558777926</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.3989904388410737</v>
+        <v>-0.4968876108532407</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.03827369009156353</v>
+        <v>-0.3338943843960937</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.9246856730381118</v>
+        <v>-0.749900741875557</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.9676015627742678</v>
+        <v>1.150736379720146</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1332163617255058</v>
+        <v>-0.1513408946895802</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.6621060037911654</v>
+        <v>0.653422710353628</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.4181544591794409</v>
+        <v>-0.3023361470050429</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.1180393932827865</v>
+        <v>0.1236929973206072</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.2196442842808409</v>
+        <v>0.0180403008196079</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.01635510214372636</v>
+        <v>0.05209517548785509</v>
       </c>
       <c r="BK6" t="n">
-        <v>-1.105022353027134</v>
+        <v>-1.26505428104044</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.3404404847209464</v>
+        <v>-0.6269934183009578</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1497870616839571</v>
+        <v>0.2636075360427875</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.3332346919293597</v>
+        <v>-0.2148866053817988</v>
       </c>
       <c r="BO6" t="n">
-        <v>-1.299172744229772</v>
+        <v>-1.068782219451679</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.2973204242776319</v>
+        <v>-0.2226020304056328</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.4691670178599862</v>
+        <v>-0.9039330303644733</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.1876935683053722</v>
+        <v>0.08781317831990917</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.3073006920646115</v>
+        <v>-0.2224629413719575</v>
       </c>
       <c r="BT6" t="n">
-        <v>1.90389219782086</v>
+        <v>1.830112461820231</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.01727886115728648</v>
+        <v>0.006946329192231973</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.3236871773370408</v>
+        <v>0.1870154894166837</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.6339331206556962</v>
+        <v>-0.3426725274904015</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.3011998982823155</v>
+        <v>-0.2123672813065609</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.4735150544381036</v>
+        <v>-0.4660172029733944</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.5842059994905909</v>
+        <v>-0.9272708118255184</v>
       </c>
       <c r="CA6" t="n">
-        <v>-1.17957480674381</v>
+        <v>-0.4000150818191813</v>
       </c>
       <c r="CB6" t="n">
-        <v>2.814121611250465</v>
+        <v>3.053161018276367</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.1444893690611326</v>
+        <v>-0.3333045758920909</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.1308669936624622</v>
+        <v>-0.02062187072473077</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.199488323699308</v>
+        <v>1.248738602982693</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.1737859280537898</v>
+        <v>0.5544970080681269</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.7537717694051768</v>
+        <v>-0.7211967582142598</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.5673150558549642</v>
+        <v>-0.6413349672000886</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.5807797336156207</v>
+        <v>-0.8352403113051803</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.05443955166627242</v>
+        <v>0.4203834014952858</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.1581923181430266</v>
+        <v>-0.1564743633614557</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.6973890089434778</v>
+        <v>0.08943702460192011</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.091430595806141</v>
+        <v>0.8684653731728924</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.5872144886902321</v>
+        <v>-0.5671897593397754</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.6462266209386371</v>
+        <v>-0.6514127030761891</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.4386862936039967</v>
+        <v>-0.5042643612351797</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.3513831216474204</v>
+        <v>-0.07726543917886367</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.5993447034488638</v>
+        <v>-0.6854931047342163</v>
       </c>
       <c r="CS6" t="n">
-        <v>-1.315947763719357</v>
+        <v>-1.172948604635788</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1188969550826492</v>
+        <v>0.08522194741437801</v>
       </c>
       <c r="CU6" t="n">
-        <v>-1.996852146215135</v>
+        <v>-1.767657759764868</v>
       </c>
       <c r="CV6" t="n">
-        <v>-1.758625219584558</v>
+        <v>-1.284566552707946</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.6311731528947069</v>
+        <v>-0.4832115102233925</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.6982628734581529</v>
+        <v>0.3946610229264209</v>
       </c>
       <c r="CY6" t="n">
-        <v>5.31589587008353</v>
+        <v>5.636365958171871</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-1.071119664677512</v>
+        <v>-1.55546547144032</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.05616394084385092</v>
+        <v>0.2586418409398351</v>
       </c>
       <c r="DB6" t="n">
-        <v>-1.251363544954366</v>
+        <v>-1.237218839631783</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.5572777839701927</v>
+        <v>-0.6227619832711927</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.718458364892484</v>
+        <v>1.687024156151894</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.6008770679629285</v>
+        <v>0.6054196810559134</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.3045906994197769</v>
+        <v>-0.5124988638355882</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.231733505794922</v>
+        <v>1.325258172381949</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.111354089979041</v>
+        <v>1.277100682756288</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.2774517417649895</v>
+        <v>-0.1109943838526532</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.5390617755861771</v>
+        <v>-0.5245909955614906</v>
       </c>
       <c r="DK6" t="n">
-        <v>-1.344466932709059</v>
+        <v>-1.140326169769487</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.02188564865293035</v>
+        <v>-0.156148393418248</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.3595579904165304</v>
+        <v>0.6382766304031242</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.01397149014481771</v>
+        <v>-0.2857791358104123</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.1433232152851127</v>
+        <v>-0.03592293542919749</v>
       </c>
       <c r="DP6" t="n">
-        <v>1.302488185252023</v>
+        <v>1.173548397152494</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.6063389252338198</v>
+        <v>0.4605823616475335</v>
       </c>
       <c r="DR6" t="n">
-        <v>1.196100876423039</v>
+        <v>1.470765677246356</v>
       </c>
       <c r="DS6" t="n">
-        <v>1.377500752563974</v>
+        <v>1.423514687732043</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.2807114622574047</v>
+        <v>0.1641489118802808</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.662261406856275</v>
+        <v>0.6034723280821225</v>
       </c>
       <c r="DV6" t="n">
-        <v>1.195501608483637</v>
+        <v>0.7502755999008114</v>
       </c>
       <c r="DW6" t="n">
-        <v>-1.430353560986837</v>
+        <v>-1.07098288780425</v>
       </c>
       <c r="DX6" t="n">
-        <v>1.263670930158982</v>
+        <v>1.121161002510189</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.8128936703884809</v>
+        <v>0.9251332432380809</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.1797771377467341</v>
+        <v>-0.4413925871592916</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.1505898796813419</v>
+        <v>-0.01159397027917811</v>
       </c>
       <c r="EB6" t="n">
-        <v>-1.04147588624609</v>
+        <v>-1.091789638739414</v>
       </c>
       <c r="EC6" t="n">
-        <v>-1.33417693470979</v>
+        <v>-1.627825079651376</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.7269372580846662</v>
+        <v>-0.4828741339322819</v>
       </c>
       <c r="EE6" t="n">
-        <v>1.147657740805204</v>
+        <v>1.088781800083611</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.007058308673590355</v>
+        <v>0.1731685332859704</v>
       </c>
       <c r="EG6" t="n">
-        <v>-1.324211220851273</v>
+        <v>-1.268839462452293</v>
       </c>
     </row>
   </sheetData>
